--- a/reference/origins/product info/WA_Topicals_Regulatory_Audited_Patch_Weights_Simplified.xlsx
+++ b/reference/origins/product info/WA_Topicals_Regulatory_Audited_Patch_Weights_Simplified.xlsx
@@ -726,9 +726,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S2">
-        <f>"Net Wt. "&amp;TEXT(M2,"0.##")&amp;" oz ("&amp;TEXT(O2,"0.#")&amp;" "&amp;P2&amp;")"</f>
-        <v/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Net Wt. 2. oz (56.7 g)</t>
+        </is>
       </c>
       <c r="T2" s="14" t="inlineStr">
         <is>
@@ -825,9 +826,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S3">
-        <f>"Net Wt. "&amp;TEXT(M3,"0.##")&amp;" oz ("&amp;TEXT(O3,"0.#")&amp;" "&amp;P3&amp;")"</f>
-        <v/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Net Wt. 3.4 oz (96.4 g)</t>
+        </is>
       </c>
       <c r="T3" s="14" t="inlineStr">
         <is>
@@ -924,9 +926,10 @@
           <t>https://cannabrands.com/dispensaries/washington/valley/access-canibus-llc?category=topical</t>
         </is>
       </c>
-      <c r="S4">
-        <f>"Net Wt. "&amp;TEXT(M4,"0.##")&amp;" oz ("&amp;TEXT(O4,"0.#")&amp;" "&amp;P4&amp;")"</f>
-        <v/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Net Wt. 3.4 oz (96.4 g)</t>
+        </is>
       </c>
       <c r="T4" s="14" t="inlineStr">
         <is>
@@ -1023,9 +1026,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S5">
-        <f>"Net Wt. "&amp;TEXT(M5,"0.##")&amp;" oz ("&amp;TEXT(O5,"0.#")&amp;" "&amp;P5&amp;")"</f>
-        <v/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Net Wt. 3.4 oz (96.4 g)</t>
+        </is>
       </c>
       <c r="T5" s="14" t="inlineStr">
         <is>
@@ -1122,9 +1126,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S6">
-        <f>"Net Wt. "&amp;TEXT(M6,"0.##")&amp;" oz ("&amp;TEXT(O6,"0.#")&amp;" "&amp;P6&amp;")"</f>
-        <v/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Net Wt. 3.4 oz (96.4 g)</t>
+        </is>
       </c>
       <c r="T6" s="14" t="inlineStr">
         <is>
@@ -1221,9 +1226,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S7">
-        <f>"Net Wt. "&amp;TEXT(M7,"0.##")&amp;" oz ("&amp;TEXT(O7,"0.#")&amp;" "&amp;P7&amp;")"</f>
-        <v/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Net Wt. 3.4 oz (96.4 g)</t>
+        </is>
       </c>
       <c r="T7" s="14" t="inlineStr">
         <is>
@@ -1316,9 +1322,10 @@
         </is>
       </c>
       <c r="R8" s="14" t="str"/>
-      <c r="S8">
-        <f>"Net Wt. "&amp;TEXT(M8,"0.##")&amp;" oz ("&amp;TEXT(O8,"0.#")&amp;" g)"</f>
-        <v/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Net Wt. 0.1 oz (2.8 g)</t>
+        </is>
       </c>
       <c r="T8" s="14" t="inlineStr">
         <is>
@@ -1415,9 +1422,10 @@
           <t>https://weedmaps.com/dispensaries/sea-change-cannabis-3/wellness/topicals</t>
         </is>
       </c>
-      <c r="S9">
-        <f>"Net Wt. "&amp;TEXT(M9,"0.##")&amp;" oz ("&amp;TEXT(O9,"0.#")&amp;" "&amp;P9&amp;")"</f>
-        <v/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Net Wt. 4. oz (113.4 g)</t>
+        </is>
       </c>
       <c r="T9" s="14" t="inlineStr">
         <is>
@@ -1514,9 +1522,10 @@
           <t>https://fairwindscannabis.com/product/flow-cream/</t>
         </is>
       </c>
-      <c r="S10">
-        <f>"Net Vol. "&amp;TEXT(M10,"0.##")&amp;" fl oz ("&amp;TEXT(O10,"0.#")&amp;" "&amp;P10&amp;")"</f>
-        <v/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Net Vol. 1.67 fl oz (50. mL)</t>
+        </is>
       </c>
       <c r="T10" s="14" t="inlineStr">
         <is>
@@ -1613,9 +1622,10 @@
           <t>https://menu.fairwindsmanufacturing.com/</t>
         </is>
       </c>
-      <c r="S11">
-        <f>"Net Vol. "&amp;TEXT(M11,"0.##")&amp;" fl oz ("&amp;TEXT(O11,"0.#")&amp;" "&amp;P11&amp;")"</f>
-        <v/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Net Vol. 3.4 fl oz (100. mL)</t>
+        </is>
       </c>
       <c r="T11" s="14" t="inlineStr">
         <is>
@@ -1709,9 +1719,10 @@
           <t>https://menu.fairwindsmanufacturing.com/</t>
         </is>
       </c>
-      <c r="S12">
-        <f>"Net Vol. "&amp;TEXT(M12,"0.##")&amp;" fl oz ("&amp;TEXT(O12,"0.#")&amp;" "&amp;P12&amp;")"</f>
-        <v/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Net Vol. 1.67 fl oz (50. mL)</t>
+        </is>
       </c>
       <c r="T12" s="14" t="inlineStr">
         <is>
@@ -1805,9 +1816,10 @@
           <t>https://menu.fairwindsmanufacturing.com/</t>
         </is>
       </c>
-      <c r="S13">
-        <f>"Net Vol. "&amp;TEXT(M13,"0.##")&amp;" fl oz ("&amp;TEXT(O13,"0.#")&amp;" "&amp;P13&amp;")"</f>
-        <v/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Net Vol. 1.67 fl oz (50. mL)</t>
+        </is>
       </c>
       <c r="T13" s="14" t="inlineStr">
         <is>
@@ -1904,9 +1916,10 @@
           <t>https://menu.fairwindsmanufacturing.com/</t>
         </is>
       </c>
-      <c r="S14">
-        <f>"Net Vol. "&amp;TEXT(M14,"0.##")&amp;" fl oz ("&amp;TEXT(O14,"0.#")&amp;" "&amp;P14&amp;")"</f>
-        <v/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
       </c>
       <c r="T14" s="14" t="inlineStr">
         <is>
@@ -2008,9 +2021,10 @@
           <t>https://menu.fairwindsmanufacturing.com/</t>
         </is>
       </c>
-      <c r="S15">
-        <f>"Net Vol. "&amp;TEXT(M15,"0.##")&amp;" fl oz ("&amp;TEXT(O15,"0.#")&amp;" "&amp;P15&amp;")"</f>
-        <v/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Net Vol. 3.4 fl oz (100. mL)</t>
+        </is>
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
@@ -2104,9 +2118,10 @@
           <t>https://menu.fairwindsmanufacturing.com/</t>
         </is>
       </c>
-      <c r="S16">
-        <f>"Net Vol. "&amp;TEXT(M16,"0.##")&amp;" fl oz ("&amp;TEXT(O16,"0.#")&amp;" "&amp;P16&amp;")"</f>
-        <v/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
@@ -2203,9 +2218,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S17">
-        <f>"Net Vol. "&amp;TEXT(M17,"0.##")&amp;" fl oz ("&amp;TEXT(O17,"0.#")&amp;" "&amp;P17&amp;")"</f>
-        <v/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Net Vol. 3.4 fl oz (100. mL)</t>
+        </is>
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
@@ -2302,9 +2318,10 @@
           <t>https://weedmaps.com/brands/marys-medicinals/products/gear/topicals</t>
         </is>
       </c>
-      <c r="S18">
-        <f>"Net Wt. "&amp;TEXT(M18,"0.##")&amp;" oz ("&amp;TEXT(O18,"0.#")&amp;" "&amp;P18&amp;")"</f>
-        <v/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Net Wt. 2. oz (56.7 g)</t>
+        </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
@@ -2401,9 +2418,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S19">
-        <f>"Net Wt. "&amp;TEXT(M19,"0.##")&amp;" oz ("&amp;TEXT(O19,"0.#")&amp;" "&amp;P19&amp;")"</f>
-        <v/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Net Wt. 2. oz (56.7 g)</t>
+        </is>
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
@@ -2500,9 +2518,10 @@
           <t>https://www.thereefstores.com/locations/bremerton/categories/topicals</t>
         </is>
       </c>
-      <c r="S20">
-        <f>"Net Wt. "&amp;TEXT(M20,"0.##")&amp;" oz ("&amp;TEXT(O20,"0.#")&amp;" "&amp;P20&amp;")"</f>
-        <v/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Net Wt. 3. oz (85. g)</t>
+        </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
@@ -2601,9 +2620,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S21">
-        <f>"Net Vol. "&amp;TEXT(M21,"0.##")&amp;" fl oz ("&amp;TEXT(O21,"0.#")&amp;" "&amp;P21&amp;")"</f>
-        <v/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Net Vol. 3.4 fl oz (100. mL)</t>
+        </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
@@ -2693,9 +2713,10 @@
         </is>
       </c>
       <c r="R22" s="14" t="str"/>
-      <c r="S22">
-        <f>"Net Wt. "&amp;TEXT(M22,"0.##")&amp;" oz ("&amp;TEXT(O22,"0.#")&amp;" g)"</f>
-        <v/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Net Wt. 0.1 oz (2.8 g)</t>
+        </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
@@ -2788,9 +2809,10 @@
         </is>
       </c>
       <c r="R23" s="14" t="str"/>
-      <c r="S23">
-        <f>"Net Wt. "&amp;TEXT(M23,"0.##")&amp;" oz ("&amp;TEXT(O23,"0.#")&amp;" g)"</f>
-        <v/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Net Wt. 0.1 oz (2.8 g)</t>
+        </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
@@ -2887,9 +2909,10 @@
           <t>https://weedmaps.com/brands/marys-medicinals/products/gear/topicals</t>
         </is>
       </c>
-      <c r="S24">
-        <f>"Net Wt. "&amp;TEXT(M24,"0.##")&amp;" oz ("&amp;TEXT(O24,"0.#")&amp;" "&amp;P24&amp;")"</f>
-        <v/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Net Wt. 2. oz (56.7 g)</t>
+        </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
@@ -2986,9 +3009,10 @@
           <t>https://weedmaps.com/brands/marys-medicinals/products/gear/topicals</t>
         </is>
       </c>
-      <c r="S25">
-        <f>"Net Vol. "&amp;TEXT(M25,"0.##")&amp;" fl oz ("&amp;TEXT(O25,"0.#")&amp;" "&amp;P25&amp;")"</f>
-        <v/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
@@ -3090,9 +3114,10 @@
           <t>https://weedmaps.com/brands/marys-medicinals/products/gear/topicals</t>
         </is>
       </c>
-      <c r="S26">
-        <f>"Net Wt. "&amp;TEXT(M26,"0.##")&amp;" oz ("&amp;TEXT(O26,"0.#")&amp;" "&amp;P26&amp;")"</f>
-        <v/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Net Wt. 2. oz (56.7 g)</t>
+        </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
@@ -3186,9 +3211,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S27">
-        <f>"Net Vol. "&amp;TEXT(M27,"0.##")&amp;" fl oz ("&amp;TEXT(O27,"0.#")&amp;" "&amp;P27&amp;")"</f>
-        <v/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Net Vol. 3.4 fl oz (100. mL)</t>
+        </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
@@ -3282,9 +3308,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S28">
-        <f>"Net Wt. "&amp;TEXT(M28,"0.##")&amp;" oz ("&amp;TEXT(O28,"0.#")&amp;" "&amp;P28&amp;")"</f>
-        <v/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Net Wt. 2. oz (56.7 g)</t>
+        </is>
       </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
@@ -3381,9 +3408,10 @@
           <t>https://weedmaps.com/brands/marys-medicinals/products/gear/topicals</t>
         </is>
       </c>
-      <c r="S29">
-        <f>"Net Wt. "&amp;TEXT(M29,"0.##")&amp;" oz ("&amp;TEXT(O29,"0.#")&amp;" "&amp;P29&amp;")"</f>
-        <v/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Net Wt. 2. oz (56.7 g)</t>
+        </is>
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
@@ -3480,9 +3508,10 @@
           <t>https://thebakereeseattle.com/menu/topical</t>
         </is>
       </c>
-      <c r="S30">
-        <f>"Net Vol. "&amp;TEXT(M30,"0.##")&amp;" fl oz ("&amp;TEXT(O30,"0.#")&amp;" "&amp;P30&amp;")"</f>
-        <v/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
       </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
@@ -3579,9 +3608,10 @@
           <t>https://thebakereeseattle.com/menu/topical</t>
         </is>
       </c>
-      <c r="S31">
-        <f>"Net Vol. "&amp;TEXT(M31,"0.##")&amp;" fl oz ("&amp;TEXT(O31,"0.#")&amp;" "&amp;P31&amp;")"</f>
-        <v/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Net Vol. 1.7 fl oz (50. mL)</t>
+        </is>
       </c>
       <c r="T31" s="14" t="inlineStr">
         <is>
@@ -3683,9 +3713,10 @@
           <t>https://weedmaps.com/brands/marys-medicinals/products/gear/topicals</t>
         </is>
       </c>
-      <c r="S32">
-        <f>"Net Wt. "&amp;TEXT(M32,"0.##")&amp;" oz ("&amp;TEXT(O32,"0.#")&amp;" "&amp;P32&amp;")"</f>
-        <v/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Net Wt. 2. oz (56.7 g)</t>
+        </is>
       </c>
       <c r="T32" s="14" t="inlineStr">
         <is>
@@ -3779,9 +3810,10 @@
           <t>https://menu.fairwindsmanufacturing.com/</t>
         </is>
       </c>
-      <c r="S33">
-        <f>"Net Vol. "&amp;TEXT(M33,"0.##")&amp;" fl oz ("&amp;TEXT(O33,"0.#")&amp;" "&amp;P33&amp;")"</f>
-        <v/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
       </c>
       <c r="T33" s="14" t="inlineStr">
         <is>
@@ -3875,9 +3907,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S34">
-        <f>"Net Wt. "&amp;TEXT(M34,"0.##")&amp;" oz ("&amp;TEXT(O34,"0.#")&amp;" "&amp;P34&amp;")"</f>
-        <v/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Net Wt. 1. oz (28.4 g)</t>
+        </is>
       </c>
       <c r="T34" s="14" t="inlineStr">
         <is>
@@ -3974,9 +4007,10 @@
           <t>https://seattle.betterhashtag.com/menus/topical</t>
         </is>
       </c>
-      <c r="S35">
-        <f>"Net Vol. "&amp;TEXT(M35,"0.##")&amp;" fl oz ("&amp;TEXT(O35,"0.#")&amp;" "&amp;P35&amp;")"</f>
-        <v/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Net Vol. 3.4 fl oz (100. mL)</t>
+        </is>
       </c>
       <c r="T35" s="14" t="inlineStr">
         <is>
@@ -4073,9 +4107,10 @@
           <t>https://www.thereefstores.com/locations/bremerton/categories/topicals</t>
         </is>
       </c>
-      <c r="S36">
-        <f>"Net Wt. "&amp;TEXT(M36,"0.##")&amp;" oz ("&amp;TEXT(O36,"0.#")&amp;" "&amp;P36&amp;")"</f>
-        <v/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Net Wt. 0.5 oz (14.2 g)</t>
+        </is>
       </c>
       <c r="T36" s="14" t="inlineStr">
         <is>
@@ -4234,6 +4269,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>

--- a/reference/origins/product info/WA_Topicals_Regulatory_Audited_Patch_Weights_Simplified.xlsx
+++ b/reference/origins/product info/WA_Topicals_Regulatory_Audited_Patch_Weights_Simplified.xlsx
@@ -56,7 +56,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -103,6 +103,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -634,14 +637,14 @@
           <t>Regulatory Audit Note</t>
         </is>
       </c>
-      <c r="U1" s="21" t="inlineStr">
-        <is>
-          <t>THC Serving/Application Review</t>
-        </is>
-      </c>
-      <c r="V1" s="21" t="inlineStr">
-        <is>
-          <t>Minimum Applications at ≤10mg THC</t>
+      <c r="U1" s="24" t="inlineStr">
+        <is>
+          <t>Topical Regulatory Basis</t>
+        </is>
+      </c>
+      <c r="V1" s="24" t="inlineStr">
+        <is>
+          <t>Unit Count (metadata)</t>
         </is>
       </c>
       <c r="W1" s="22" t="inlineStr">
@@ -738,11 +741,8 @@
       </c>
       <c r="U2" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -838,11 +838,8 @@
       </c>
       <c r="U3" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -938,11 +935,8 @@
       </c>
       <c r="U4" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1038,11 +1032,8 @@
       </c>
       <c r="U5" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1138,11 +1129,8 @@
       </c>
       <c r="U6" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1238,11 +1226,8 @@
       </c>
       <c r="U7" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1334,11 +1319,11 @@
       </c>
       <c r="U8" s="14" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED: one listed patch contains more than 10mg THC. If one patch is one serving/application, this exceeds the general-use 10mg active Δ9-THC serving limit. Confirm licensed WA product classification/medical-compliant status before production use.</t>
+          <t>Regulated by NET QUANTITY as a cannabis topical (WAC 314-55-105(7)), the same basis as every other row here (Jack, 2026-09-22). Patch COUNT is shopper-facing metadata and does not replace the net-quantity declaration, and the package THC total is not treated as a per-serving figure.</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1434,11 +1419,8 @@
       </c>
       <c r="U9" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1534,11 +1516,8 @@
       </c>
       <c r="U10" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1634,7 +1613,7 @@
       </c>
       <c r="U11" s="14" t="inlineStr">
         <is>
-          <t>No listed THC; 10mg THC serving limit not triggered by this catalog value</t>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1731,7 +1710,7 @@
       </c>
       <c r="U12" s="14" t="inlineStr">
         <is>
-          <t>No listed THC; 10mg THC serving limit not triggered by this catalog value</t>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1828,11 +1807,8 @@
       </c>
       <c r="U13" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1928,11 +1904,8 @@
       </c>
       <c r="U14" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 5 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>5</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2033,7 +2006,7 @@
       </c>
       <c r="U15" s="14" t="inlineStr">
         <is>
-          <t>No listed THC; 10mg THC serving limit not triggered by this catalog value</t>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2130,11 +2103,8 @@
       </c>
       <c r="U16" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2230,11 +2200,8 @@
       </c>
       <c r="U17" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2330,11 +2297,8 @@
       </c>
       <c r="U18" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2430,11 +2394,8 @@
       </c>
       <c r="U19" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2530,7 +2491,7 @@
       </c>
       <c r="U20" s="14" t="inlineStr">
         <is>
-          <t>No listed THC; 10mg THC serving limit not triggered by this catalog value</t>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2632,7 +2593,7 @@
       </c>
       <c r="U21" s="14" t="inlineStr">
         <is>
-          <t>No listed THC; 10mg THC serving limit not triggered by this catalog value</t>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2725,11 +2686,11 @@
       </c>
       <c r="U22" s="14" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED: one listed patch contains more than 10mg THC. If one patch is one serving/application, this exceeds the general-use 10mg active Δ9-THC serving limit. Confirm licensed WA product classification/medical-compliant status before production use.</t>
+          <t>Regulated by NET QUANTITY as a cannabis topical (WAC 314-55-105(7)), the same basis as every other row here (Jack, 2026-09-22). Patch COUNT is shopper-facing metadata and does not replace the net-quantity declaration, and the package THC total is not treated as a per-serving figure.</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2821,11 +2782,11 @@
       </c>
       <c r="U23" s="14" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED: one listed patch contains more than 10mg THC. If one patch is one serving/application, this exceeds the general-use 10mg active Δ9-THC serving limit. Confirm licensed WA product classification/medical-compliant status before production use.</t>
+          <t>Regulated by NET QUANTITY as a cannabis topical (WAC 314-55-105(7)), the same basis as every other row here (Jack, 2026-09-22). Patch COUNT is shopper-facing metadata and does not replace the net-quantity declaration, and the package THC total is not treated as a per-serving figure.</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2921,11 +2882,8 @@
       </c>
       <c r="U24" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3021,11 +2979,8 @@
       </c>
       <c r="U25" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 5 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>5</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3126,7 +3081,7 @@
       </c>
       <c r="U26" s="14" t="inlineStr">
         <is>
-          <t>No listed THC; 10mg THC serving limit not triggered by this catalog value</t>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3223,7 +3178,7 @@
       </c>
       <c r="U27" s="14" t="inlineStr">
         <is>
-          <t>No listed THC; 10mg THC serving limit not triggered by this catalog value</t>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3320,11 +3275,8 @@
       </c>
       <c r="U28" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3420,11 +3372,8 @@
       </c>
       <c r="U29" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3520,11 +3469,8 @@
       </c>
       <c r="U30" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 5 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>5</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3620,11 +3566,8 @@
       </c>
       <c r="U31" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 5 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>5</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3725,7 +3668,7 @@
       </c>
       <c r="U32" s="14" t="inlineStr">
         <is>
-          <t>No listed THC; 10mg THC serving limit not triggered by this catalog value</t>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -3822,7 +3765,7 @@
       </c>
       <c r="U33" s="14" t="inlineStr">
         <is>
-          <t>No listed THC; 10mg THC serving limit not triggered by this catalog value</t>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -3919,11 +3862,8 @@
       </c>
       <c r="U34" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4019,11 +3959,8 @@
       </c>
       <c r="U35" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 10 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>10</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4119,11 +4056,8 @@
       </c>
       <c r="U36" s="14" t="inlineStr">
         <is>
-          <t>Package total alone does not establish serving/application compliance. At least 5 applications would be needed for ≤10mg THC per application if THC were evenly apportioned.</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>5</v>
+          <t>Regulated by NET QUANTITY under the cannabis-topical labeling subsection (WAC 314-55-105(7)): net weight in oz + g, or volume as applicable. The subsection does not require a serving size or servings-per-package declaration, so this catalog does not apportion the package THC into servings.</t>
+        </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4269,7 +4203,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
@@ -4449,44 +4382,44 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>THC serving/application</t>
+          <t>Regulatory basis</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Not fully auditable</t>
+          <t>Resolved 2026-09-22</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>A single serving of a cannabis-infused product may not exceed 10 mg active delta-9 THC; package total alone does not define topical application size.</t>
+          <t>Cannabis topicals are declared and limited by net quantity. The topical labeling subsection requires net weight in oz + g or volume as applicable and does not require a serving-size declaration, so a package THC total is not a per-serving figure for this product class.</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>https://app.leg.wa.gov/wac/default.aspx?cite=314-55-095</t>
+          <t>https://app.leg.wa.gov/wac/default.aspx?cite=314-55-105</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Single-patch rows</t>
+          <t>Transdermal patches</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Review required</t>
+          <t>Resolved 2026-09-22</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>A one-patch SKU above 10 mg THC needs verification of its Washington licensed classification / applicable compliant-medical framework before being treated as general-use compliant.</t>
+          <t>Patches are treated as cannabis topicals and measured BY WEIGHT, not by dose (Jack, 2026-09-22). Each carries its own net-weight declaration; patch count is metadata beside it. The earlier REVIEW REQUIRED flag applied the edible 10 mg per-serving rule to a topical and is withdrawn.</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>https://app.leg.wa.gov/wac/default.aspx?cite=314-55-095</t>
+          <t>https://app.leg.wa.gov/wac/default.aspx?cite=314-55-105</t>
         </is>
       </c>
     </row>
